--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15733,7 +15733,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -87464,8 +87464,8 @@
       <c r="G2320" s="9">
         <v>588000</v>
       </c>
-      <c r="H2320" s="6" t="s">
-        <v>45</v>
+      <c r="H2320" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J2320" s="9">
         <f t="shared" si="75"/>
@@ -87495,8 +87495,8 @@
       <c r="G2321" s="9">
         <v>448154</v>
       </c>
-      <c r="H2321" s="5" t="s">
-        <v>5080</v>
+      <c r="H2321" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J2321" s="9">
         <f t="shared" si="75"/>
@@ -87588,8 +87588,8 @@
       <c r="G2324" s="9">
         <v>1386000</v>
       </c>
-      <c r="H2324" s="5" t="s">
-        <v>5080</v>
+      <c r="H2324" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J2324" s="9">
         <f t="shared" si="75"/>
@@ -97140,7 +97140,7 @@
         <v>547</v>
       </c>
       <c r="E2633" s="9">
-        <f t="shared" ref="E2633:E2696" si="84">SUM(G2633/(1+(F2633/100)) /(1+(37/100)))</f>
+        <f t="shared" ref="E2633:E2658" si="84">SUM(G2633/(1+(F2633/100)) /(1+(37/100)))</f>
         <v>11333.775713337756</v>
       </c>
       <c r="F2633" s="3">
@@ -97153,7 +97153,7 @@
         <v>16</v>
       </c>
       <c r="J2633" s="9">
-        <f t="shared" ref="J2633:J2696" si="85">SUM(E2633* I2633)</f>
+        <f t="shared" ref="J2633:J2658" si="85">SUM(E2633* I2633)</f>
         <v>0</v>
       </c>
     </row>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15394,7 +15394,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15733,7 +15733,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -63265,8 +63265,8 @@
       <c r="G1539" s="9">
         <v>322000</v>
       </c>
-      <c r="H1539" s="5" t="s">
-        <v>5080</v>
+      <c r="H1539" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1539" s="9">
         <f t="shared" si="49"/>
@@ -63575,8 +63575,8 @@
       <c r="G1549" s="9">
         <v>392000</v>
       </c>
-      <c r="H1549" s="5" t="s">
-        <v>5080</v>
+      <c r="H1549" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1549" s="9">
         <f t="shared" si="51"/>
@@ -64629,8 +64629,8 @@
       <c r="G1583" s="9">
         <v>2226000</v>
       </c>
-      <c r="H1583" s="4" t="s">
-        <v>16</v>
+      <c r="H1583" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1583" s="9">
         <f t="shared" si="51"/>
@@ -67605,8 +67605,8 @@
       <c r="G1679" s="9">
         <v>252000</v>
       </c>
-      <c r="H1679" s="4" t="s">
-        <v>16</v>
+      <c r="H1679" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1679" s="9">
         <f t="shared" si="55"/>
@@ -70643,8 +70643,8 @@
       <c r="G1777" s="9">
         <v>2030000</v>
       </c>
-      <c r="H1777" s="4" t="s">
-        <v>16</v>
+      <c r="H1777" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1777" s="9">
         <f t="shared" si="57"/>
@@ -70798,8 +70798,8 @@
       <c r="G1782" s="9">
         <v>3290000</v>
       </c>
-      <c r="H1782" s="5" t="s">
-        <v>5080</v>
+      <c r="H1782" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1782" s="9">
         <f t="shared" si="57"/>
@@ -70860,8 +70860,8 @@
       <c r="G1784" s="9">
         <v>5166000</v>
       </c>
-      <c r="H1784" s="4" t="s">
-        <v>16</v>
+      <c r="H1784" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1784" s="9">
         <f t="shared" si="57"/>
@@ -71635,8 +71635,8 @@
       <c r="G1809" s="9">
         <v>3290000</v>
       </c>
-      <c r="H1809" s="5" t="s">
-        <v>5080</v>
+      <c r="H1809" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1809" s="9">
         <f t="shared" si="59"/>
@@ -72534,8 +72534,8 @@
       <c r="G1838" s="9">
         <v>3626000</v>
       </c>
-      <c r="H1838" s="4" t="s">
-        <v>16</v>
+      <c r="H1838" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1838" s="9">
         <f t="shared" si="59"/>
@@ -73309,8 +73309,8 @@
       <c r="G1863" s="9">
         <v>2716000</v>
       </c>
-      <c r="H1863" s="4" t="s">
-        <v>16</v>
+      <c r="H1863" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1863" s="9">
         <f t="shared" si="59"/>
@@ -73340,8 +73340,8 @@
       <c r="G1864" s="9">
         <v>2632000</v>
       </c>
-      <c r="H1864" s="4" t="s">
-        <v>16</v>
+      <c r="H1864" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1864" s="9">
         <f t="shared" si="59"/>
@@ -74267,8 +74267,8 @@
       <c r="G1894" s="9">
         <v>1302000</v>
       </c>
-      <c r="H1894" s="4" t="s">
-        <v>16</v>
+      <c r="H1894" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1894" s="9">
         <f t="shared" si="61"/>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15394,7 +15394,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15733,7 +15733,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -54817,8 +54817,8 @@
       <c r="G1266" s="9">
         <v>1330000</v>
       </c>
-      <c r="H1266" s="6" t="s">
-        <v>45</v>
+      <c r="H1266" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1266" s="9">
         <f t="shared" si="41"/>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15430,7 +15430,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -70888,16 +70888,16 @@
       </c>
       <c r="E1784" s="9">
         <f t="shared" si="56"/>
-        <v>1224588.2849731555</v>
+        <v>1089461.3018037039</v>
       </c>
       <c r="F1784" s="3">
         <v>21</v>
       </c>
       <c r="G1784" s="9">
-        <v>2030000</v>
-      </c>
-      <c r="H1784" s="4" t="s">
-        <v>16</v>
+        <v>1806000</v>
+      </c>
+      <c r="H1784" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1784" s="9">
         <f t="shared" si="57"/>
@@ -70919,16 +70919,16 @@
       </c>
       <c r="E1785" s="9">
         <f t="shared" si="56"/>
-        <v>1224588.2849731555</v>
+        <v>1089461.3018037039</v>
       </c>
       <c r="F1785" s="3">
         <v>21</v>
       </c>
       <c r="G1785" s="9">
-        <v>2030000</v>
-      </c>
-      <c r="H1785" s="4" t="s">
-        <v>16</v>
+        <v>1806000</v>
+      </c>
+      <c r="H1785" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1785" s="9">
         <f t="shared" si="57"/>
@@ -70950,16 +70950,16 @@
       </c>
       <c r="E1786" s="9">
         <f t="shared" si="56"/>
-        <v>1224588.2849731555</v>
+        <v>1089461.3018037039</v>
       </c>
       <c r="F1786" s="3">
         <v>21</v>
       </c>
       <c r="G1786" s="9">
-        <v>2030000</v>
-      </c>
-      <c r="H1786" s="4" t="s">
-        <v>16</v>
+        <v>1806000</v>
+      </c>
+      <c r="H1786" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1786" s="9">
         <f t="shared" si="57"/>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15769,7 +15769,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45960</v>
+        <v>45962</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -47825,8 +47825,8 @@
       <c r="G1039" s="9">
         <v>1106000</v>
       </c>
-      <c r="H1039" s="5" t="s">
-        <v>5080</v>
+      <c r="H1039" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1039" s="9">
         <f t="shared" si="35"/>
@@ -58155,8 +58155,8 @@
       <c r="G1373" s="9">
         <v>36400</v>
       </c>
-      <c r="H1373" s="4" t="s">
-        <v>16</v>
+      <c r="H1373" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1373" s="9">
         <f t="shared" si="45"/>
@@ -58186,8 +58186,8 @@
       <c r="G1374" s="9">
         <v>36400</v>
       </c>
-      <c r="H1374" s="4" t="s">
-        <v>16</v>
+      <c r="H1374" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1374" s="9">
         <f t="shared" si="45"/>
@@ -58806,8 +58806,8 @@
       <c r="G1394" s="9">
         <v>1666000</v>
       </c>
-      <c r="H1394" s="4" t="s">
-        <v>16</v>
+      <c r="H1394" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1394" s="9">
         <f t="shared" si="45"/>
@@ -58829,13 +58829,13 @@
       </c>
       <c r="E1395" s="9">
         <f t="shared" si="44"/>
-        <v>320926.58502744767</v>
+        <v>325149.30325149302</v>
       </c>
       <c r="F1395" s="3">
         <v>21</v>
       </c>
       <c r="G1395" s="9">
-        <v>532000</v>
+        <v>539000</v>
       </c>
       <c r="H1395" s="6" t="s">
         <v>45</v>
@@ -58860,13 +58860,13 @@
       </c>
       <c r="E1396" s="9">
         <f t="shared" si="44"/>
-        <v>481389.8775411715</v>
+        <v>515171.6233335344</v>
       </c>
       <c r="F1396" s="3">
         <v>21</v>
       </c>
       <c r="G1396" s="9">
-        <v>798000</v>
+        <v>854000</v>
       </c>
       <c r="H1396" s="6" t="s">
         <v>45</v>
@@ -58992,8 +58992,8 @@
       <c r="G1400" s="9">
         <v>364000</v>
       </c>
-      <c r="H1400" s="4" t="s">
-        <v>16</v>
+      <c r="H1400" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1400" s="9">
         <f t="shared" si="45"/>
@@ -59023,8 +59023,8 @@
       <c r="G1401" s="9">
         <v>364000</v>
       </c>
-      <c r="H1401" s="4" t="s">
-        <v>16</v>
+      <c r="H1401" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1401" s="9">
         <f t="shared" si="45"/>
@@ -59046,13 +59046,13 @@
       </c>
       <c r="E1402" s="9">
         <f t="shared" si="44"/>
-        <v>287144.83923508477</v>
+        <v>312481.1485793569</v>
       </c>
       <c r="F1402" s="3">
         <v>21</v>
       </c>
       <c r="G1402" s="9">
-        <v>476000</v>
+        <v>518000</v>
       </c>
       <c r="H1402" s="6" t="s">
         <v>45</v>
@@ -59077,13 +59077,13 @@
       </c>
       <c r="E1403" s="9">
         <f t="shared" si="44"/>
-        <v>287144.83923508477</v>
+        <v>312481.1485793569</v>
       </c>
       <c r="F1403" s="3">
         <v>21</v>
       </c>
       <c r="G1403" s="9">
-        <v>476000</v>
+        <v>518000</v>
       </c>
       <c r="H1403" s="6" t="s">
         <v>45</v>
@@ -59139,16 +59139,16 @@
       </c>
       <c r="E1405" s="9">
         <f t="shared" si="44"/>
-        <v>418049.10418049101</v>
+        <v>456053.56819689932</v>
       </c>
       <c r="F1405" s="3">
         <v>21</v>
       </c>
       <c r="G1405" s="9">
-        <v>693000</v>
-      </c>
-      <c r="H1405" s="4" t="s">
-        <v>16</v>
+        <v>756000</v>
+      </c>
+      <c r="H1405" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1405" s="9">
         <f t="shared" si="45"/>
@@ -59170,16 +59170,16 @@
       </c>
       <c r="E1406" s="9">
         <f t="shared" si="44"/>
-        <v>418049.10418049101</v>
+        <v>456053.56819689932</v>
       </c>
       <c r="F1406" s="3">
         <v>21</v>
       </c>
       <c r="G1406" s="9">
-        <v>693000</v>
-      </c>
-      <c r="H1406" s="4" t="s">
-        <v>16</v>
+        <v>756000</v>
+      </c>
+      <c r="H1406" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1406" s="9">
         <f t="shared" si="45"/>
@@ -59201,13 +59201,13 @@
       </c>
       <c r="E1407" s="9">
         <f t="shared" si="44"/>
-        <v>354708.33081981057</v>
+        <v>325149.30325149302</v>
       </c>
       <c r="F1407" s="3">
         <v>21</v>
       </c>
       <c r="G1407" s="9">
-        <v>588000</v>
+        <v>539000</v>
       </c>
       <c r="H1407" s="6" t="s">
         <v>45</v>
@@ -59232,16 +59232,16 @@
       </c>
       <c r="E1408" s="9">
         <f t="shared" si="44"/>
-        <v>481389.8775411715</v>
+        <v>515171.6233335344</v>
       </c>
       <c r="F1408" s="3">
         <v>21</v>
       </c>
       <c r="G1408" s="9">
-        <v>798000</v>
-      </c>
-      <c r="H1408" s="4" t="s">
-        <v>16</v>
+        <v>854000</v>
+      </c>
+      <c r="H1408" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1408" s="9">
         <f t="shared" si="45"/>
@@ -59697,16 +59697,16 @@
       </c>
       <c r="E1423" s="9">
         <f t="shared" si="46"/>
-        <v>1313265.3676781082</v>
+        <v>1418833.3232792423</v>
       </c>
       <c r="F1423" s="3">
         <v>21</v>
       </c>
       <c r="G1423" s="9">
-        <v>2177000</v>
-      </c>
-      <c r="H1423" s="4" t="s">
-        <v>16</v>
+        <v>2352000</v>
+      </c>
+      <c r="H1423" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J1423" s="9">
         <f t="shared" si="47"/>
@@ -73686,8 +73686,8 @@
       <c r="G1874" s="9">
         <v>1610000</v>
       </c>
-      <c r="H1874" s="5" t="s">
-        <v>5080</v>
+      <c r="H1874" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1874" s="9">
         <f t="shared" si="61"/>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15314,7 +15314,7 @@
     <numFmt numFmtId="164" formatCode="#0.00"/>
     <numFmt numFmtId="165" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15326,6 +15326,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -15381,7 +15389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -15393,6 +15401,7 @@
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15430,7 +15439,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15769,7 +15778,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45962</v>
+        <v>45966</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -18380,8 +18389,8 @@
       <c r="G88" s="9">
         <v>644000</v>
       </c>
-      <c r="H88" s="5" t="s">
-        <v>5080</v>
+      <c r="H88" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J88" s="9">
         <f t="shared" si="5"/>
@@ -24838,8 +24847,8 @@
       <c r="G297" s="9">
         <v>7280</v>
       </c>
-      <c r="H297" s="6" t="s">
-        <v>45</v>
+      <c r="H297" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J297" s="9">
         <f t="shared" si="11"/>
@@ -30055,7 +30064,7 @@
       </c>
     </row>
     <row r="466" spans="1:10">
-      <c r="A466" t="s">
+      <c r="A466" s="11" t="s">
         <v>3608</v>
       </c>
       <c r="B466" t="s">
@@ -31255,8 +31264,8 @@
       <c r="G504" s="9">
         <v>1008000</v>
       </c>
-      <c r="H504" s="5" t="s">
-        <v>5080</v>
+      <c r="H504" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J504" s="9">
         <f t="shared" si="17"/>
@@ -31286,8 +31295,8 @@
       <c r="G505" s="9">
         <v>1008000</v>
       </c>
-      <c r="H505" s="5" t="s">
-        <v>5080</v>
+      <c r="H505" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J505" s="9">
         <f t="shared" si="17"/>
@@ -52469,8 +52478,8 @@
       <c r="G1189" s="9">
         <v>190274</v>
       </c>
-      <c r="H1189" s="5" t="s">
-        <v>5080</v>
+      <c r="H1189" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1189" s="9">
         <f t="shared" si="39"/>
@@ -55721,8 +55730,8 @@
       <c r="G1294" s="9">
         <v>87360</v>
       </c>
-      <c r="H1294" s="5" t="s">
-        <v>5080</v>
+      <c r="H1294" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1294" s="9">
         <f t="shared" si="43"/>
@@ -55814,8 +55823,8 @@
       <c r="G1297" s="9">
         <v>110600</v>
       </c>
-      <c r="H1297" s="6" t="s">
-        <v>45</v>
+      <c r="H1297" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1297" s="9">
         <f t="shared" si="43"/>
@@ -60573,8 +60582,8 @@
       <c r="G1451" s="9">
         <v>84000</v>
       </c>
-      <c r="H1451" s="6" t="s">
-        <v>45</v>
+      <c r="H1451" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1451" s="9">
         <f t="shared" si="47"/>
@@ -60604,8 +60613,8 @@
       <c r="G1452" s="9">
         <v>112000</v>
       </c>
-      <c r="H1452" s="6" t="s">
-        <v>45</v>
+      <c r="H1452" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1452" s="9">
         <f t="shared" si="47"/>
@@ -71020,8 +71029,8 @@
       <c r="G1788" s="9">
         <v>3290000</v>
       </c>
-      <c r="H1788" s="6" t="s">
-        <v>45</v>
+      <c r="H1788" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1788" s="9">
         <f t="shared" si="57"/>
@@ -71082,8 +71091,8 @@
       <c r="G1790" s="9">
         <v>5166000</v>
       </c>
-      <c r="H1790" s="6" t="s">
-        <v>45</v>
+      <c r="H1790" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1790" s="9">
         <f t="shared" si="57"/>
@@ -73531,8 +73540,8 @@
       <c r="G1869" s="9">
         <v>2338000</v>
       </c>
-      <c r="H1869" s="6" t="s">
-        <v>45</v>
+      <c r="H1869" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1869" s="9">
         <f t="shared" si="59"/>
@@ -74275,8 +74284,8 @@
       <c r="G1893" s="9">
         <v>2226000</v>
       </c>
-      <c r="H1893" s="6" t="s">
-        <v>45</v>
+      <c r="H1893" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1893" s="9">
         <f t="shared" si="61"/>
@@ -74306,8 +74315,8 @@
       <c r="G1894" s="9">
         <v>343000</v>
       </c>
-      <c r="H1894" s="5" t="s">
-        <v>5080</v>
+      <c r="H1894" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1894" s="9">
         <f t="shared" si="61"/>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15339,7 +15339,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -15376,6 +15376,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -15389,7 +15395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -15402,6 +15408,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15778,7 +15785,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -74498,8 +74505,8 @@
       <c r="G1900" s="9">
         <v>1302000</v>
       </c>
-      <c r="H1900" s="6" t="s">
-        <v>45</v>
+      <c r="H1900" s="12" t="s">
+        <v>5080</v>
       </c>
       <c r="J1900" s="9">
         <f t="shared" si="61"/>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15785,7 +15785,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -24203,8 +24203,8 @@
       <c r="G276" s="9">
         <v>14000</v>
       </c>
-      <c r="H276" s="6" t="s">
-        <v>45</v>
+      <c r="H276" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J276" s="9">
         <f t="shared" si="11"/>
@@ -54559,8 +54559,8 @@
       <c r="G1256" s="9">
         <v>616000</v>
       </c>
-      <c r="H1256" s="5" t="s">
-        <v>5080</v>
+      <c r="H1256" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1256" s="9">
         <f t="shared" si="41"/>
@@ -70943,8 +70943,8 @@
       <c r="G1785" s="9">
         <v>1806000</v>
       </c>
-      <c r="H1785" s="6" t="s">
-        <v>45</v>
+      <c r="H1785" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1785" s="9">
         <f t="shared" si="57"/>
@@ -70974,8 +70974,8 @@
       <c r="G1786" s="9">
         <v>1806000</v>
       </c>
-      <c r="H1786" s="6" t="s">
-        <v>45</v>
+      <c r="H1786" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1786" s="9">
         <f t="shared" si="57"/>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15463,7 +15463,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15801,7 +15801,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -47454,8 +47454,8 @@
       <c r="G1026" s="9">
         <v>1793792</v>
       </c>
-      <c r="H1026" s="5" t="s">
-        <v>5103</v>
+      <c r="H1026" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1026" s="9">
         <f t="shared" si="31"/>
@@ -47485,8 +47485,8 @@
       <c r="G1027" s="9">
         <v>1470000</v>
       </c>
-      <c r="H1027" s="5" t="s">
-        <v>5103</v>
+      <c r="H1027" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1027" s="9">
         <f t="shared" si="31"/>
@@ -47516,8 +47516,8 @@
       <c r="G1028" s="9">
         <v>1820000</v>
       </c>
-      <c r="H1028" s="5" t="s">
-        <v>5103</v>
+      <c r="H1028" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J1028" s="9">
         <f t="shared" si="31"/>
@@ -87380,8 +87380,8 @@
       <c r="G2315" s="9">
         <v>546000</v>
       </c>
-      <c r="H2315" s="5" t="s">
-        <v>5103</v>
+      <c r="H2315" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J2315" s="9">
         <f t="shared" si="73"/>
@@ -87904,8 +87904,8 @@
       <c r="G2332" s="9">
         <v>588000</v>
       </c>
-      <c r="H2332" s="6" t="s">
-        <v>44</v>
+      <c r="H2332" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J2332" s="9">
         <f t="shared" si="73"/>

--- a/public_db/IMSA_DB.xlsx
+++ b/public_db/IMSA_DB.xlsx
@@ -15463,7 +15463,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15801,7 +15801,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -33085,8 +33085,8 @@
       <c r="G562" s="9">
         <v>518000</v>
       </c>
-      <c r="H562" s="6" t="s">
-        <v>44</v>
+      <c r="H562" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J562" s="9">
         <f t="shared" si="17"/>
@@ -33674,8 +33674,8 @@
       <c r="G581" s="9">
         <v>672000</v>
       </c>
-      <c r="H581" s="6" t="s">
-        <v>44</v>
+      <c r="H581" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J581" s="9">
         <f t="shared" si="17"/>
@@ -33705,8 +33705,8 @@
       <c r="G582" s="9">
         <v>672000</v>
       </c>
-      <c r="H582" s="5" t="s">
-        <v>5103</v>
+      <c r="H582" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="J582" s="9">
         <f t="shared" si="17"/>
